--- a/Methodology/PIRNN/01-PWM-Theta/Ts-03/Resumo_Estatisticas.xlsx
+++ b/Methodology/PIRNN/01-PWM-Theta/Ts-03/Resumo_Estatisticas.xlsx
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9054818043084298</v>
+        <v>0.9187495989313105</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0106942690259208</v>
+        <v>0.008695608747086825</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0215753498491221</v>
+        <v>0.01854675510479305</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002441144733314561</v>
+        <v>0.001984917290229408</v>
       </c>
     </row>
     <row r="3">
@@ -687,16 +687,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8609925117259538</v>
+        <v>0.8665123130858144</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004173895895393956</v>
+        <v>0.001960731218447745</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03173586425903538</v>
+        <v>0.03047567555360368</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0009529140855090103</v>
+        <v>0.0004476413506187291</v>
       </c>
     </row>
     <row r="4">
@@ -711,16 +711,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5489814036066261</v>
+        <v>0.6915264180806749</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1234661829166727</v>
+        <v>0.0527294351187563</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1476092284611434</v>
+        <v>0.100957139665352</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04040797463144293</v>
+        <v>0.01725727341912744</v>
       </c>
     </row>
     <row r="5">
@@ -735,16 +735,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.887523457412405</v>
+        <v>0.9115222901286376</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01883554907521428</v>
+        <v>0.01121499849414486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02583800711563448</v>
+        <v>0.02032501750710322</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004326884876046546</v>
+        <v>0.002576299059582794</v>
       </c>
     </row>
     <row r="6">
@@ -759,16 +759,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8876112520513036</v>
+        <v>0.8932029072816962</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004756756452838573</v>
+        <v>0.003549178652056762</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02665423090095659</v>
+        <v>0.02532810820318029</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00112811724614506</v>
+        <v>0.0008417268545766765</v>
       </c>
     </row>
     <row r="7">
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7456334340906368</v>
+        <v>0.7736320130318376</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02191088706496448</v>
+        <v>0.01480490240150757</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08362235828222339</v>
+        <v>0.07441789703062761</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007203148109805687</v>
+        <v>0.00486707381737171</v>
       </c>
     </row>
   </sheetData>

--- a/Methodology/PIRNN/01-PWM-Theta/Ts-03/Resumo_Estatisticas.xlsx
+++ b/Methodology/PIRNN/01-PWM-Theta/Ts-03/Resumo_Estatisticas.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Todos_Modelos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Top_10_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Top_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Melhor_Modelo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,7 +522,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-4.640774263797782</v>
+        <v>-4.640774263797781</v>
       </c>
       <c r="D4" t="n">
         <v>3.518223739933758</v>
@@ -596,13 +597,13 @@
         <v>-1.065809059187464</v>
       </c>
       <c r="D7" t="n">
-        <v>2.234356302867807</v>
+        <v>2.234356302867808</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6791294471915427</v>
+        <v>0.6791294471915428</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7345389226787459</v>
+        <v>0.7345389226787458</v>
       </c>
     </row>
   </sheetData>
@@ -663,16 +664,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9187495989313105</v>
+        <v>0.9054818043084298</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008695608747086825</v>
+        <v>0.0106942690259208</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01854675510479305</v>
+        <v>0.0215753498491221</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001984917290229408</v>
+        <v>0.002441144733314561</v>
       </c>
     </row>
     <row r="3">
@@ -687,16 +688,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8665123130858144</v>
+        <v>0.8609925117259538</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001960731218447745</v>
+        <v>0.004173895895393956</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03047567555360368</v>
+        <v>0.03173586425903538</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004476413506187291</v>
+        <v>0.0009529140855090103</v>
       </c>
     </row>
     <row r="4">
@@ -711,16 +712,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6915264180806749</v>
+        <v>0.5489814036066261</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0527294351187563</v>
+        <v>0.1234661829166727</v>
       </c>
       <c r="E4" t="n">
-        <v>0.100957139665352</v>
+        <v>0.1476092284611434</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01725727341912744</v>
+        <v>0.04040797463144293</v>
       </c>
     </row>
     <row r="5">
@@ -735,16 +736,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9115222901286376</v>
+        <v>0.887523457412405</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01121499849414486</v>
+        <v>0.01883554907521428</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02032501750710322</v>
+        <v>0.02583800711563448</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002576299059582794</v>
+        <v>0.004326884876046546</v>
       </c>
     </row>
     <row r="6">
@@ -759,16 +760,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8932029072816962</v>
+        <v>0.8876112520513036</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003549178652056762</v>
+        <v>0.004756756452838573</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02532810820318029</v>
+        <v>0.02665423090095659</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008417268545766765</v>
+        <v>0.00112811724614506</v>
       </c>
     </row>
     <row r="7">
@@ -783,16 +784,207 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7736320130318376</v>
+        <v>0.7456334340906368</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01480490240150757</v>
+        <v>0.02191088706496448</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07441789703062761</v>
+        <v>0.08362235828222339</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00486707381737171</v>
+        <v>0.007203148109805687</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Neurons</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Best_R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Theta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Train_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>model_32_16_8_Ld0.7_Lp0.3_r0.01_seed0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[32, 16, 8]</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9279762550595982</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Theta</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Train_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>model_264_128_Ld0.7_Lp0.3_r0.5_seed0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[264, 128]</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.868291627641418</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Theta</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>model_264_Ld0.3_Lp0.7_r0.9_seed1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[16, 8, 4]</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.752384537930381</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Theta</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Test_1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>model_32_16_8_Ld0.3_Lp0.7_r0.01_seed0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[32, 16, 8]</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9203841418818819</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Theta</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Test_2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>model_16_8_4_Ld0.3_Lp0.7_r0.5_seed2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[16, 8, 4]</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8971528709909345</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Theta</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Test_3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>model_16_8_Ld0.3_Lp0.7_r0.01_seed0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[16, 8]</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7877008399175166</v>
       </c>
     </row>
   </sheetData>
